--- a/data/chinese/P2T3_Chapter14.xlsx
+++ b/data/chinese/P2T3_Chapter14.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DE673C-4771-FA4D-BC68-AD439D7DE826}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5148147-6CAA-D446-B297-DC72D479A9F5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,127 +60,141 @@
     <t>智能</t>
   </si>
   <si>
-    <t>具備思考、判斷、處理資訊的能力</t>
-  </si>
-  <si>
     <t>智能機器可以自動完成許多工作。</t>
   </si>
   <si>
     <t>識別</t>
   </si>
   <si>
-    <t>辨認、分辨出人或事物</t>
-  </si>
-  <si>
     <t>這台儀器能快速識別不同的物品。</t>
   </si>
   <si>
     <t>技術</t>
   </si>
   <si>
-    <t>專門的方法、技能與工藝</t>
-  </si>
-  <si>
     <t>先進的技術讓工作變得更簡單。</t>
   </si>
   <si>
     <t>倉庫</t>
   </si>
   <si>
-    <t>用來存放貨物、物品的地方</t>
-  </si>
-  <si>
     <t>貨物都整齊地擺放在倉庫裡。</t>
   </si>
   <si>
     <t>效率</t>
   </si>
   <si>
-    <t>單位時間內完成工作的速度與成果</t>
-  </si>
-  <si>
     <t>自動化作業大幅提高了工作效率。</t>
   </si>
   <si>
     <t>研究</t>
   </si>
   <si>
-    <t>深入探討、鑽研問題與知識</t>
-  </si>
-  <si>
     <t>科學家不斷研究新的發明與應用。</t>
   </si>
   <si>
     <t>機械</t>
   </si>
   <si>
-    <t>利用動力運作的器具、裝置</t>
-  </si>
-  <si>
     <t>工廠裡有各式各樣的機械在運轉。</t>
   </si>
   <si>
     <t>整理</t>
   </si>
   <si>
-    <t>收拾、歸納，使變得整齊有序</t>
-  </si>
-  <si>
     <t>工人忙著整理倉庫裡的貨品。</t>
   </si>
   <si>
     <t>程式</t>
   </si>
   <si>
-    <t>電腦執行的指令組合、程序</t>
-  </si>
-  <si>
     <t>工程師編寫新程式來控制機器。</t>
   </si>
   <si>
     <t>悄悄</t>
   </si>
   <si>
-    <t>聲音輕微、行動不讓人察覺</t>
-  </si>
-  <si>
     <t>他悄悄走進車間，觀察機器運作。</t>
   </si>
   <si>
     <t>提升</t>
   </si>
   <si>
-    <t>提高、往上增進</t>
-  </si>
-  <si>
     <t>改良設備能有效提升生產速度。</t>
   </si>
   <si>
     <t>製造</t>
   </si>
   <si>
-    <t>加工生產各類物品、產品</t>
-  </si>
-  <si>
     <t>這間工廠專門製造自動化機械。</t>
   </si>
   <si>
     <t>無窮</t>
   </si>
   <si>
-    <t>沒有盡頭、數量極多</t>
-  </si>
-  <si>
     <t>科學的世界藏著無窮的新知識。</t>
   </si>
   <si>
     <t>挑選</t>
   </si>
   <si>
-    <t>從多數當中揀選合適的</t>
-  </si>
-  <si>
     <t>我們仔細挑選品質優良的零件。</t>
+  </si>
+  <si>
+    <t>會自己思考、判斷、做事的能力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辨認出東西是什麼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做事的方法、本領</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用來放東西的大房間或地方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做事做得又快又好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仔細想、查資料，弄清楚事情的道理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用零件組成、會動的機器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>把東西排好、收拾乾淨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>給電腦或機器人的指令，讓它們照著做事，像一套操作步驟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聲音很小、不讓人發現</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>變得更好、更高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做出東西來</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很多很多，永遠用不完、數不完</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>從很多東西裡，選出自己喜歡或需要的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -859,7 +873,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="53.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="101.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="71.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -894,10 +908,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -906,13 +920,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -921,13 +935,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -936,13 +950,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -951,13 +965,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -966,13 +980,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -981,13 +995,13 @@
     </row>
     <row r="8" spans="1:11" ht="27">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -996,13 +1010,13 @@
     </row>
     <row r="9" spans="1:11" ht="27">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -1011,13 +1025,13 @@
     </row>
     <row r="10" spans="1:11" ht="27">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -1026,13 +1040,13 @@
     </row>
     <row r="11" spans="1:11" ht="27">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -1041,13 +1055,13 @@
     </row>
     <row r="12" spans="1:11" ht="27">
       <c r="A12" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -1056,13 +1070,13 @@
     </row>
     <row r="13" spans="1:11" ht="27">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3">
         <v>3</v>
@@ -1071,13 +1085,13 @@
     </row>
     <row r="14" spans="1:11" ht="27">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3">
         <v>3</v>
@@ -1086,13 +1100,13 @@
     </row>
     <row r="15" spans="1:11" ht="27">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3">
         <v>3</v>
